--- a/光伏配储项目/电价数据/2026/鹤山站.xlsx
+++ b/光伏配储项目/电价数据/2026/鹤山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51622</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.93667</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5962799999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.76467</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6075700000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45421</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26037</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.49479</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.17035</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22813</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.09495999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19493</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.18041</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02485</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.08075</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18496</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24194</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26758</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23358</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.06504</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.16638</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.56738</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.06917</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.15017</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.09518</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.8796499999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.52559</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6100099999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.73651</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6781200000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.94251</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.09588</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.8607100000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.2046</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.61393</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9125700000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.76201</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.53044</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.87052</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.80087</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.84411</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8181499999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.57145</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42233</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.85538</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.79752</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.83602</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.87173</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53744</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5196799999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7240800000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44039</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.5924299999999999</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.6794600000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.5229299999999999</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.45977</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.6666299999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.70297</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.9918400000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.6256</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.6799500000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.5663400000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.9673200000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7190299999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.47741</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.56074</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.79618</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5647300000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.49337</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.55257</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.56014</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.6454099999999999</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.55799</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.48382</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.71746</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.50547</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.9849600000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.14441</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06027</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.88413</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9656399999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.12403</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.81853</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.89354</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.11226</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.32866</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.49655</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.65239</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33354</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.47455</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56796</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.77827</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.6573099999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.74433</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.50148</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.56353</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.5555099999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5627799999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5823400000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.75029</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.11727</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6517000000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.77991</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.14026</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.59977</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.5432400000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46489</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.56101</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.86042</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.84053</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.77783</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.52267</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7620399999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.68579</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.9305</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61983</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6127</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.6335700000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.61963</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63574</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.57021</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.59513</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.58885</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48773</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.4974</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.48112</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.71485</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.70525</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.55391</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.23938</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.46084</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.68174</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.46285</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.6542100000000001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.78649</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45392</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46133</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53526</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.52364</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.58377</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5377799999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50931</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45573</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.47643</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.44684</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.27036</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.10456</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.10456</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.10686</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.07978</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.08945</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08258</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.00848</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.01436</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.03799</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.04865999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.00365</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.05232</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.06431000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.04772</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.00301</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.03003</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.02909</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21224</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.08212</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.08377</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08729000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.00362</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04193</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.00073</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.20363</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.10397</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.16064</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37256</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7482799999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.52435</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.12927</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04165</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03147</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12612</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00983</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.00826</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.02041</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03669</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04246</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.00253</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0008100000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.004719999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.18121</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33623</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33434</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19078</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.17852</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.23728</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.5065299999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45564</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44337</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.47641</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15391</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5423600000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79231</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.64727</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.53626</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.8185800000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9966900000000001</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.5492999999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.00093</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9652200000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.38758</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.98027</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6983200000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.29856</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.81126</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.41451</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.10809</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5844600000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78779</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78912</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88149</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5067900000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41744</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46553</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22454</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8793800000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6395</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54267</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50263</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5891000000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5972999999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66123</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5313099999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56548</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.9531900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.68431</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.90686</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.88822</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.90411</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.47845</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.49329</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.55064</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95645</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47706</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54553</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.51118</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.24791</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.04181</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59676</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.93026</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.42948</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19007</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70363</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79539</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6498200000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58369</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5575599999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.62525</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.49727</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.50222</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.80677</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.68091</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.7281</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.73727</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.63791</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.64883</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.43823</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.45879</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.55513</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.48791</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.47727</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.53224</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48175</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.49045</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.44479</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.74113</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.89362</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.63666</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5192100000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.4724100000000001</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32473</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.93731</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18269</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19313</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57262</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5838300000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.16932</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.17451</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.19497</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.18362</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.17488</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.16477</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.16758</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.19965</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19153</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18058</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.03823</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22887</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.4358399999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.5539700000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.53386</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.46397</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.5585599999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.51451</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.52176</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.51048</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.6859400000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67323</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.46333</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.56684</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.79547</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.77967</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.65965</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.65235</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.71978</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.18699</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.7499199999999999</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.4992200000000001</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.53224</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.50373</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.6519299999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.63502</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.6684099999999999</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.68175</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.67687</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.65404</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.67849</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.57062</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.7116399999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.8147300000000001</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.79296</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.7649400000000001</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.7085499999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.71628</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.72437</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.67337</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.7586499999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.50146</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.5345599999999999</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.70238</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.71074</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.70466</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.9704199999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.78406</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.10074</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.73426</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.82462</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.36964</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.07509</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.74776</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.53161</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31019</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.5575599999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.56204</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.62179</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.56213</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49657</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.7246900000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65198</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83088</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.22072</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01284</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24578</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.22172</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.18661</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.04582</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.44595</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.45701</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.5423600000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.37011</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.48219</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.50998</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.9437300000000001</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9250900000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.32752</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.27748</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.78261</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.6118</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.40931</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.47494</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.9865499999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.53378</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.75506</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.40329</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9967699999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.8915299999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5516799999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.5956399999999999</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.60753</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5428200000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.74707</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.66032</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.9028200000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50066</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41877</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.7922</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.7765599999999999</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.06276</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.13007</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.23307</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.34068</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.2933</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.15782</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.67015</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.69957</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.7898200000000001</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.5571699999999999</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.00164</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.2088</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.96327</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.63367</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.76451</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.40091</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.02632</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.51149</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.59514</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.56957</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.5414800000000001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.44715</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.51719</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.43446</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.5314800000000001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5748099999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.73166</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.6799500000000001</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.63963</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.62153</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.75875</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.01017</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.45585</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.13015</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.05174</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.80731</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.84985</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7854</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.01325</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.64577</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.72112</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5899500000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47841</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47175</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5548099999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45814</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.43321</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.44299</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5775399999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.6860299999999999</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.13775</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.18433</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.19504</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.03345</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42702</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.50735</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24765</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26448</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03753</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17989</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17759</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18824</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06088</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24836</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16861</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20723</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.45263</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.08777</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.07345</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.03315</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.18808</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03356</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.03236</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11189</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.18302</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.12096</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.04521</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.03319</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11056</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.01989</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.02647</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.08353000000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.01738</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.01671</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.02038</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.05399</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.03583</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.16771</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20624</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25103</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.26447</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.22567</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12644</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.52767</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.25426</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24628</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25655</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22672</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25171</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24835</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24466</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2566000000000001</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24452</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22083</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6072000000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.61021</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.72154</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.56799</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.45533</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.15028</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.14676</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.11567</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.07512</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.14987</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.14312</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.11786</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.01692</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13713</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.23194</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08205</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17524</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.48064</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16772</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.47261</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.48913</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.5282899999999999</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.50939</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.53237</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.91215</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6761699999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.6605700000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.69547</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.8128300000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.67662</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.70314</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.71346</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.80459</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.50113</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.54308</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.54196</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.64742</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.55574</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32887</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.41799</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1392</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.96141</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49315</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5800700000000001</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49815</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.03701</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.61611</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.5286000000000001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.61909</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.68559</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.6801799999999999</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.53974</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.55753</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.16082</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.22166</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.56029</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.5422400000000001</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.53796</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.75795</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.48807</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.55004</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.52546</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33332</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5518500000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.53873</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.77228</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.6711</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.89725</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.0019</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.53252</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.47859</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.45224</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.48598</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.28374</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.45677</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.61664</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.47476</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.15588</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.45659</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.49438</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.48712</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.51758</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.62761</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.65019</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.6970700000000001</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.76361</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.7467999999999999</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.8168200000000001</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.8292999999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.80703</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.69269</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.59673</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.69664</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.53342</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6065199999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.53474</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5705</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.54604</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.50902</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.53372</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68364</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5015299999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45719</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.47262</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.56035</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.47045</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.60173</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.60017</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.65677</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6652100000000001</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.68641</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.7545599999999999</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.50995</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.50995</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.51812</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.50085</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.50096</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25413</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.47794</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.47541</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.5478500000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.53037</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.58701</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.58936</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41903</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.61029</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.71557</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.64001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.59353</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.57429</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46513</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53864</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5204</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45721</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54789</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53271</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6643300000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.52979</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.48993</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74476</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.51164</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.51342</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49533</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.47354</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.43566</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.56426</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.46389</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.7591100000000001</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.25186</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.18254</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.13323</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.75097</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.6488400000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.17104</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.06804</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01227</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.09054999999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.06321</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24392</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.08669</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.1962</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.18141</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.23836</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.49272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.50144</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.5175700000000001</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.45614</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.17233</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.04195</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5069399999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.49254</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.52175</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.5060899999999999</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.48789</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.6194299999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37531</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.99029</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.49264</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5484199999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5909099999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.45532</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.5245700000000001</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.21798</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.07069</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07449</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.12115</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.07323</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.14259</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.19122</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.13501</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8948400000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.81455</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.64347</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.05962</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.11627</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.8278799999999999</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.56214</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.48677</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.70125</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.71473</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.52639</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.68916</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.5462100000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.57989</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5709500000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.55506</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.6041299999999999</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.60553</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.6115499999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.7244400000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.52427</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.49444</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5686100000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.66212</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.7066399999999999</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.53511</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.42628</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40217</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6607799999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.43498</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23297</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.16178</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21521</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.25586</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.22336</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.18366</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.21545</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.20222</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.12483</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14408</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17794</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18961</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22177</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16621</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.10821</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.18325</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.19784</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.20264</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.47099</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.46358</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.41759</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.42667</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.51364</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46209</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42446</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43361</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.53644</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5585399999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.50429</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.43837</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44603</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
